--- a/VerveStacks_THA_grids_kan/vt_vervestacks_THA_v1.xlsx
+++ b/VerveStacks_THA_grids_kan/vt_vervestacks_THA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_THA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{263C805A-4D51-4684-BC69-2306D6599736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6BD088A-D438-4D6C-88F5-0C3B9AAB36B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{44E40206-6C8F-4F65-88ED-2F850830EF4B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{576EAF2A-E9AD-4F11-8F6D-A9C2CC7C71B9}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2843,7 +2843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D22880D-16CF-4196-A3A3-1574654503E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0544B2AC-3EF8-4575-BB32-43572603BBE1}">
   <dimension ref="B9:V163"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12409,7 +12409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB07E22-4A2A-485A-BC1F-5E01D9E4CB06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C152AAA2-C69F-49CA-AFB1-D5330577769E}">
   <dimension ref="B9:V43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14463,7 +14463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081403C6-8034-4ACA-AB71-B1C1682D5A00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5A47F3-2197-44AF-B027-551D92343239}">
   <dimension ref="B9:V342"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25737,7 +25737,7 @@
         <v>33</v>
       </c>
       <c r="M204">
-        <v>0.20079871835314381</v>
+        <v>0.20079871835314378</v>
       </c>
       <c r="O204" t="s">
         <v>334</v>
@@ -25790,7 +25790,7 @@
         <v>33</v>
       </c>
       <c r="M205">
-        <v>0.20079871835314381</v>
+        <v>0.20079871835314378</v>
       </c>
       <c r="O205" t="s">
         <v>334</v>
@@ -25843,7 +25843,7 @@
         <v>33</v>
       </c>
       <c r="M206">
-        <v>0.20079871835314381</v>
+        <v>0.20079871835314378</v>
       </c>
       <c r="O206" t="s">
         <v>334</v>
@@ -26785,7 +26785,7 @@
         <v>14</v>
       </c>
       <c r="R221" t="s">
-        <v>345</v>
+        <v>463</v>
       </c>
       <c r="S221" t="s">
         <v>336</v>
@@ -26847,7 +26847,7 @@
         <v>14</v>
       </c>
       <c r="R222" t="s">
-        <v>463</v>
+        <v>345</v>
       </c>
       <c r="S222" t="s">
         <v>336</v>
@@ -31548,7 +31548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B9B2C2-B52D-46D1-9B65-1BB277C3D6F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6445E699-5D48-4F5F-987E-6B1644457C09}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
